--- a/xlsx/換色紀錄表(2410) 4號盤存.xlsx
+++ b/xlsx/換色紀錄表(2410) 4號盤存.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d310cb6cf3413c87/換色紀錄表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="752" documentId="8_{D2DBBC8B-7A72-EE46-B813-F1066388F35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAD974E2-54EF-441B-BA9C-758BC81A5C2F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{40FD683A-4072-C545-BEA2-DCDCBBFB510E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12576" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12576" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="庫存查詢表" sheetId="7" r:id="rId1"/>
@@ -3974,7 +3974,9 @@
     </row>
     <row r="7" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A7" s="125"/>
-      <c r="B7" s="121"/>
+      <c r="B7" s="121">
+        <v>45569</v>
+      </c>
       <c r="C7" s="27" t="s">
         <v>28</v>
       </c>
@@ -4013,7 +4015,9 @@
     </row>
     <row r="8" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A8" s="125"/>
-      <c r="B8" s="121"/>
+      <c r="B8" s="121">
+        <v>45569</v>
+      </c>
       <c r="C8" s="27" t="s">
         <v>29</v>
       </c>
@@ -4198,7 +4202,9 @@
     </row>
     <row r="13" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A13" s="125"/>
-      <c r="B13" s="121"/>
+      <c r="B13" s="121">
+        <v>45573</v>
+      </c>
       <c r="C13" s="27" t="s">
         <v>2</v>
       </c>
@@ -4237,7 +4243,9 @@
     </row>
     <row r="14" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A14" s="125"/>
-      <c r="B14" s="121"/>
+      <c r="B14" s="121">
+        <v>45573</v>
+      </c>
       <c r="C14" s="27" t="s">
         <v>29</v>
       </c>
@@ -4490,7 +4498,9 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A21" s="125"/>
-      <c r="B21" s="121"/>
+      <c r="B21" s="121">
+        <v>45579</v>
+      </c>
       <c r="C21" s="27" t="s">
         <v>34</v>
       </c>
@@ -4529,7 +4539,9 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A22" s="125"/>
-      <c r="B22" s="121"/>
+      <c r="B22" s="121">
+        <v>45579</v>
+      </c>
       <c r="C22" s="27" t="s">
         <v>29</v>
       </c>
@@ -4679,7 +4691,9 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A26" s="125"/>
-      <c r="B26" s="121"/>
+      <c r="B26" s="121">
+        <v>45582</v>
+      </c>
       <c r="C26" s="27" t="s">
         <v>33</v>
       </c>
@@ -4720,7 +4734,9 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A27" s="125"/>
-      <c r="B27" s="121"/>
+      <c r="B27" s="121">
+        <v>45582</v>
+      </c>
       <c r="C27" s="27" t="s">
         <v>29</v>
       </c>
@@ -4796,7 +4812,9 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A29" s="125"/>
-      <c r="B29" s="121"/>
+      <c r="B29" s="121">
+        <v>45583</v>
+      </c>
       <c r="C29" s="27" t="s">
         <v>37</v>
       </c>
@@ -4962,7 +4980,9 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="125"/>
-      <c r="B34" s="121"/>
+      <c r="B34" s="121">
+        <v>45587</v>
+      </c>
       <c r="C34" s="27" t="s">
         <v>29</v>
       </c>
@@ -4997,7 +5017,9 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="125"/>
-      <c r="B35" s="121"/>
+      <c r="B35" s="121">
+        <v>45587</v>
+      </c>
       <c r="C35" s="27" t="s">
         <v>25</v>
       </c>
@@ -5036,7 +5058,9 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="125"/>
-      <c r="B36" s="121"/>
+      <c r="B36" s="121">
+        <v>45587</v>
+      </c>
       <c r="C36" s="27" t="s">
         <v>2</v>
       </c>
@@ -5071,7 +5095,9 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="125"/>
-      <c r="B37" s="121"/>
+      <c r="B37" s="121">
+        <v>45587</v>
+      </c>
       <c r="C37" s="27" t="s">
         <v>39</v>
       </c>
@@ -5182,7 +5208,9 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A40" s="125"/>
-      <c r="B40" s="121"/>
+      <c r="B40" s="121">
+        <v>45589</v>
+      </c>
       <c r="C40" s="27" t="s">
         <v>37</v>
       </c>
@@ -5219,7 +5247,9 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A41" s="125"/>
-      <c r="B41" s="121"/>
+      <c r="B41" s="121">
+        <v>45589</v>
+      </c>
       <c r="C41" s="27" t="s">
         <v>25</v>
       </c>
@@ -5256,7 +5286,9 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A42" s="125"/>
-      <c r="B42" s="121"/>
+      <c r="B42" s="121">
+        <v>45589</v>
+      </c>
       <c r="C42" s="27" t="s">
         <v>2</v>
       </c>
@@ -5293,7 +5325,9 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A43" s="125"/>
-      <c r="B43" s="121"/>
+      <c r="B43" s="121">
+        <v>45589</v>
+      </c>
       <c r="C43" s="27" t="s">
         <v>29</v>
       </c>
@@ -5359,7 +5393,9 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A45" s="125"/>
-      <c r="B45" s="158"/>
+      <c r="B45" s="121">
+        <v>45590</v>
+      </c>
       <c r="C45" s="153" t="s">
         <v>39</v>
       </c>
@@ -5392,7 +5428,9 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A46" s="125"/>
-      <c r="B46" s="158"/>
+      <c r="B46" s="121">
+        <v>45590</v>
+      </c>
       <c r="C46" s="153" t="s">
         <v>37</v>
       </c>
@@ -5427,7 +5465,9 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="125"/>
-      <c r="B47" s="158"/>
+      <c r="B47" s="121">
+        <v>45590</v>
+      </c>
       <c r="C47" s="153" t="s">
         <v>25</v>
       </c>
@@ -5565,7 +5605,9 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A51" s="125"/>
-      <c r="B51" s="121"/>
+      <c r="B51" s="121">
+        <v>45593</v>
+      </c>
       <c r="C51" s="27" t="s">
         <v>37</v>
       </c>
@@ -5639,7 +5681,9 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A53" s="125"/>
-      <c r="B53" s="121"/>
+      <c r="B53" s="121">
+        <v>45594</v>
+      </c>
       <c r="C53" s="27" t="s">
         <v>33</v>
       </c>
@@ -5674,7 +5718,9 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A54" s="125"/>
-      <c r="B54" s="121"/>
+      <c r="B54" s="121">
+        <v>45594</v>
+      </c>
       <c r="C54" s="27" t="s">
         <v>25</v>
       </c>
@@ -5712,7 +5758,9 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A55" s="125"/>
-      <c r="B55" s="121"/>
+      <c r="B55" s="121">
+        <v>45594</v>
+      </c>
       <c r="C55" s="27" t="s">
         <v>29</v>
       </c>
@@ -5860,7 +5908,9 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A59" s="125"/>
-      <c r="B59" s="121"/>
+      <c r="B59" s="121">
+        <v>45597</v>
+      </c>
       <c r="C59" s="27" t="s">
         <v>29</v>
       </c>
@@ -7268,7 +7318,7 @@
       </c>
       <c r="G2" s="21">
         <f ca="1">TODAY()</f>
-        <v>45755</v>
+        <v>46300</v>
       </c>
       <c r="H2" s="54" t="e">
         <f>TEXT(WEEKDAY(每日用粉紀錄表!#REF!,1),"aaaa")</f>
